--- a/employees_GA.xlsx
+++ b/employees_GA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
   <si>
     <t>Legal Name</t>
   </si>
@@ -64,12 +64,6 @@
     <t>Diego</t>
   </si>
   <si>
-    <t>Weihe</t>
-  </si>
-  <si>
-    <t>Hongyuan</t>
-  </si>
-  <si>
     <t>Chong</t>
   </si>
   <si>
@@ -85,12 +79,6 @@
     <t>Rivera</t>
   </si>
   <si>
-    <t>Sun</t>
-  </si>
-  <si>
-    <t>Wang</t>
-  </si>
-  <si>
     <t>Xu</t>
   </si>
   <si>
@@ -106,16 +94,16 @@
     <t>Salary</t>
   </si>
   <si>
-    <t>Receiving - Receiving</t>
+    <t>Inbound - Department Inbound</t>
   </si>
   <si>
     <t>Resource - Resource Center</t>
   </si>
   <si>
-    <t>Transfer - Transfer</t>
-  </si>
-  <si>
-    <t>Shipping - Shipping</t>
+    <t>Inventory - Department Inventory</t>
+  </si>
+  <si>
+    <t>Outbound - Department Outbound</t>
   </si>
   <si>
     <t>Drop-Shipp - Drop-Shipping</t>
@@ -454,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -503,22 +491,22 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1">
         <v>46202</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -535,22 +523,22 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1">
         <v>44988</v>
       </c>
       <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
         <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -567,22 +555,22 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
         <v>46174</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
         <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -599,22 +587,22 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
       </c>
       <c r="G5" s="1">
         <v>45778</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -625,92 +613,28 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45658</v>
+      </c>
+      <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="1">
-        <v>46045</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1">
-        <v>46118</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1">
-        <v>45658</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
